--- a/final_reports/TABLA_XVIII_Metricas_Calidad_Final.xlsx
+++ b/final_reports/TABLA_XVIII_Metricas_Calidad_Final.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Métricas Calidad Final" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="TABLA XVIII - Métricas Finales" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -45,12 +45,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="0087CEEB"/>
+        <bgColor rgb="0087CEEB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0090EE90"/>
+        <bgColor rgb="0090EE90"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFE0"/>
+        <bgColor rgb="00FFFFE0"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -58,30 +70,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -484,24 +484,24 @@
           <t>Precisión OCR</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>≥80%</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>81.8%</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>82.4%</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Cumplido</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Tiempo de respuesta</t>
         </is>
@@ -516,14 +516,14 @@
           <t>0.01s</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Cumplido</t>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Superado</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Tiempo procesamiento OCR</t>
         </is>
@@ -538,7 +538,7 @@
           <t>0.01s</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Superado</t>
         </is>
@@ -550,17 +550,17 @@
           <t>Tasa de errores del sistema</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>≤5.0%</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Cumplido</t>
         </is>
@@ -572,34 +572,34 @@
           <t>Disponibilidad del sistema</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>≥95.0%</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>98.2%</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Cumplido</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Tiempo detección orientación</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>1.8s</t>
         </is>
